--- a/reviews/a-envoyer/pierre-huiban-2026-10-05.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-05.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02T06:15:02</t>
+          <t>2026-10-02T10:58:10</t>
         </is>
       </c>
     </row>

--- a/reviews/a-envoyer/pierre-huiban-2026-10-05.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-05.xlsx
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>Story lun — Lundi, on repart. LFG</t>
+          <t>Story Mon: A new week starts early</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr"/>
@@ -777,13 +777,13 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Story mar — Pas d'excuses</t>
+          <t>Story Tue: Session done before the day starts</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr"/>
       <c r="I3" s="9" t="inlineStr"/>
     </row>
-    <row r="4" ht="21" customHeight="1">
+    <row r="4" ht="156" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>PH-03</t>
@@ -791,12 +791,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Mer 07/10</t>
+          <t>Mar 06/10</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -809,20 +809,24 @@
           <t>IG</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>voir le visuel</t>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ visuel à venir</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Story mer — La donnée parle</t>
+          <t>The last seconds of our fastest race 🇮🇹
+53:34 in Rome with @antoine_bhna. First in our age group, and a new best by more than a minute.
+I still can't watch this without smiling ❤️
+Thank you Antoine 🙏
+#hyrox #hyroxrome #hyroxdoubles #roadtohongkong</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr"/>
     </row>
-    <row r="5" ht="171" customHeight="1">
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>PH-04</t>
@@ -835,7 +839,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -855,16 +859,13 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Je note tout. Chaque station, chaque tour, chaque temps de transition.
-Pas pour me faire plaisir : pour savoir où je perds. La donnée ne ment pas, elle ne motive pas non plus. Elle dit juste où travailler.
-Et en général, ce n'est pas la station que j'aurais choisie.
-#hyrox #hyroxtraining #data #roadtohongkong</t>
+          <t>Story Wed: The numbers tell me where to work</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr"/>
     </row>
-    <row r="6" ht="21" customHeight="1">
+    <row r="6" ht="210" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>PH-05</t>
@@ -872,17 +873,17 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Jeu 08/10</t>
+          <t>Mer 07/10</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Carrousel (8 visuels)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -897,7 +898,13 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Story jeu — Ça brûle ?</t>
+          <t>Rome. 53:34 🇮🇹
+Our fastest race yet, and first in our age group (35-39) with @antoine_bhna. 12th of 292 teams in Pro Doubles Men.
+Swipe for the race, station by station: where we found time, and the one station that still costs us.
+Saturday night in Rome was special. Thank you Antoine for every second of it ❤️
+Next stop: the World Championships in Hong Kong, June 2027 🙏
+Which number surprises you the most? I read everything.
+#hyrox #hyroxrome #hyroxdoubles #roadtohongkong #hyroxworldchampionships</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr"/>
@@ -911,7 +918,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Ven 09/10</t>
+          <t>Jeu 08/10</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -936,13 +943,13 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Story ven — Encore une séance</t>
+          <t>Story Thu: One station at a time</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr"/>
     </row>
-    <row r="8" ht="21" customHeight="1">
+    <row r="8" ht="171" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>PH-07</t>
@@ -950,12 +957,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Sam 10/10</t>
+          <t>Jeu 08/10</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -968,20 +975,24 @@
           <t>IG</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>voir le visuel</t>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ visuel à venir</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Story sam — Samedi = volume</t>
+          <t>Station eight. 100 wall balls. Legs completely empty.
+3:22 in Rome, our best-ranked station of the day (10th of 292).
+Nobody is fresh here. It's just about not stopping 🙏
+How do you get through your last 30 reps? I read everything.
+#hyrox #wallballs #hyroxrome #roadtohongkong</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr"/>
       <c r="I8" s="9" t="inlineStr"/>
     </row>
-    <row r="9" ht="171" customHeight="1">
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>PH-08</t>
@@ -989,12 +1000,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Sam 10/10</t>
+          <t>Ven 09/10</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1014,11 +1025,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Commercial la semaine, en déplacement une partie du temps. Papa le reste. Athlète entre les deux.
-Les séances se calent à 5h30 ou elles ne se calent pas. Il n'y a pas de créneau parfait, il y a celui qu'on prend.
-La fatigue fait partie du plan. L'excuse, non.
-LFG.
-#hyrox #doublevie #hyroxfrance #roadtohongkong</t>
+          <t>Story Fri: One more session before the weekend</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr"/>
@@ -1032,7 +1039,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Dim 11/10</t>
+          <t>Sam 10/10</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1057,15 +1064,97 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Story dim — Récup</t>
+          <t>Story Sat: Training, then family time</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr"/>
     </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>PH-10</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Dim 11/10</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Story Sun: Recovery is part of the plan</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="156" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>PH-11</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Dim 11/10</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ visuel à venir</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Everyone films the stations. Nobody films the running.
+But in HYROX, it's 8 kilometres. In Rome we ran them in 27:59, 18th of 292 teams.
+That's where most of our progress this season came from 🙏
+Runners or station people: which one are you?
+#hyrox #hyroxrunning #hyroxrome #roadtohongkong</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <conditionalFormatting sqref="A2:I10">
+  <conditionalFormatting sqref="A2:I12">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="✅ OK pour publier"</formula>
     </cfRule>
@@ -1077,20 +1166,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choisir dans la liste" error="Choisissez une des trois décisions du menu, ou laissez la case vide." type="list">
+    <dataValidation sqref="H2:H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choisir dans la liste" error="Choisissez une des trois décisions du menu, ou laissez la case vide." type="list">
       <formula1>"✅ OK pour publier,✏️ À corriger (voir commentaire),⛔ Ne pas publier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1102,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,7 +1225,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02T10:58:10</t>
+          <t>2026-10-05T10:38:23</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1263,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>383261227</v>
+        <v>388274841</v>
       </c>
       <c r="C6" t="n">
         <v>6572293</v>
@@ -1187,7 +1275,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Story lun — Lundi, on repart. LFG</t>
+          <t>Story Mon: A new week starts early</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1286,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>383261247</v>
+        <v>388274872</v>
       </c>
       <c r="C7" t="n">
         <v>6572293</v>
@@ -1210,7 +1298,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Story mar — Pas d'excuses</t>
+          <t>Story Tue: Session done before the day starts</t>
         </is>
       </c>
     </row>
@@ -1221,19 +1309,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>383261260</v>
+        <v>388353555</v>
       </c>
       <c r="C8" t="n">
         <v>6572293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-07T06:00:00</t>
+          <t>2026-10-06T12:30:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Story mer — La donnée parle</t>
+          <t>The last seconds of our fastest race 🇮🇹
+53:34 in Rome with @antoine_bhna. First in our age group, and a new best by more than a minute.
+I still can't watch this without smiling ❤️
+Thank you Antoine 🙏
+#hyrox #hyroxrome #hyroxdoubles #roadtohongkong</t>
         </is>
       </c>
     </row>
@@ -1244,22 +1336,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>383268870</v>
+        <v>388274905</v>
       </c>
       <c r="C9" t="n">
         <v>6572293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-07T18:00:00</t>
+          <t>2026-10-07T06:00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Je note tout. Chaque station, chaque tour, chaque temps de transition.
-Pas pour me faire plaisir : pour savoir où je perds. La donnée ne ment pas, elle ne motive pas non plus. Elle dit juste où travailler.
-Et en général, ce n'est pas la station que j'aurais choisie.
-#hyrox #hyroxtraining #data #roadtohongkong</t>
+          <t>Story Wed: The numbers tell me where to work</t>
         </is>
       </c>
     </row>
@@ -1270,19 +1359,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>383261271</v>
+        <v>388353493</v>
       </c>
       <c r="C10" t="n">
         <v>6572293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-08T06:00:00</t>
+          <t>2026-10-07T18:00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Story jeu — Ça brûle ?</t>
+          <t>Rome. 53:34 🇮🇹
+Our fastest race yet, and first in our age group (35-39) with @antoine_bhna. 12th of 292 teams in Pro Doubles Men.
+Swipe for the race, station by station: where we found time, and the one station that still costs us.
+Saturday night in Rome was special. Thank you Antoine for every second of it ❤️
+Next stop: the World Championships in Hong Kong, June 2027 🙏
+Which number surprises you the most? I read everything.
+#hyrox #hyroxrome #hyroxdoubles #roadtohongkong #hyroxworldchampionships</t>
         </is>
       </c>
     </row>
@@ -1293,19 +1388,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>383261288</v>
+        <v>388274941</v>
       </c>
       <c r="C11" t="n">
         <v>6572293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-09T06:00:00</t>
+          <t>2026-10-08T06:00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Story ven — Encore une séance</t>
+          <t>Story Thu: One station at a time</t>
         </is>
       </c>
     </row>
@@ -1316,19 +1411,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>383262078</v>
+        <v>388250065</v>
       </c>
       <c r="C12" t="n">
         <v>6572293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-10T06:00:00</t>
+          <t>2026-10-08T12:30:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Story sam — Samedi = volume</t>
+          <t>Station eight. 100 wall balls. Legs completely empty.
+3:22 in Rome, our best-ranked station of the day (10th of 292).
+Nobody is fresh here. It's just about not stopping 🙏
+How do you get through your last 30 reps? I read everything.
+#hyrox #wallballs #hyroxrome #roadtohongkong</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1438,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>383268897</v>
+        <v>388274961</v>
       </c>
       <c r="C13" t="n">
         <v>6572293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-10T09:00:00</t>
+          <t>2026-10-09T06:00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Commercial la semaine, en déplacement une partie du temps. Papa le reste. Athlète entre les deux.
-Les séances se calent à 5h30 ou elles ne se calent pas. Il n'y a pas de créneau parfait, il y a celui qu'on prend.
-La fatigue fait partie du plan. L'excuse, non.
-LFG.
-#hyrox #doublevie #hyroxfrance #roadtohongkong</t>
+          <t>Story Fri: One more session before the weekend</t>
         </is>
       </c>
     </row>
@@ -1366,19 +1461,69 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>383262095</v>
+        <v>388274993</v>
       </c>
       <c r="C14" t="n">
         <v>6572293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-10-10T06:00:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Story Sat: Training, then family time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PH-10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>388275014</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6572293</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2026-10-11T06:00:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Story dim — Récup</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Story Sun: Recovery is part of the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PH-11</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>388250071</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6572293</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-11T18:00:00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Everyone films the stations. Nobody films the running.
+But in HYROX, it's 8 kilometres. In Rome we ran them in 27:59, 18th of 292 teams.
+That's where most of our progress this season came from 🙏
+Runners or station people: which one are you?
+#hyrox #hyroxrunning #hyroxrome #roadtohongkong</t>
         </is>
       </c>
     </row>

--- a/reviews/a-envoyer/pierre-huiban-2026-10-05.xlsx
+++ b/reviews/a-envoyer/pierre-huiban-2026-10-05.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05T10:38:23</t>
+          <t>2026-10-05T13:13:38</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>388274841</v>
+        <v>388533717</v>
       </c>
       <c r="C6" t="n">
         <v>6572293</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>388274872</v>
+        <v>388533737</v>
       </c>
       <c r="C7" t="n">
         <v>6572293</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>388274905</v>
+        <v>388533766</v>
       </c>
       <c r="C9" t="n">
         <v>6572293</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>388274941</v>
+        <v>388533789</v>
       </c>
       <c r="C11" t="n">
         <v>6572293</v>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>388274961</v>
+        <v>388533840</v>
       </c>
       <c r="C13" t="n">
         <v>6572293</v>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>388274993</v>
+        <v>388533861</v>
       </c>
       <c r="C14" t="n">
         <v>6572293</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>388275014</v>
+        <v>388533890</v>
       </c>
       <c r="C15" t="n">
         <v>6572293</v>
